--- a/GUA/Waste/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
+++ b/GUA/Waste/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClimateLeadGroup\Desktop\CLG_repositories\openmodels_lac\GUA\Modelos\Residuos\A2_Extra_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClimateLeadGroup\Downloads\Waste_GUA_v1_2025\A2_Extra_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7869BC05-BBDE-4008-8FC3-F47C74E31CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38FBEAF-E71C-4D74-B17C-9B439B9232A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,16 +56,16 @@
     <t>Region</t>
   </si>
   <si>
+    <t>Mode_of_Operation</t>
+  </si>
+  <si>
+    <t>Timeslice</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
     <t>GUA</t>
-  </si>
-  <si>
-    <t>Mode_of_Operation</t>
-  </si>
-  <si>
-    <t>Timeslice</t>
-  </si>
-  <si>
-    <t>All</t>
   </si>
 </sst>
 </file>
@@ -89,13 +89,19 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -241,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -261,6 +267,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -546,8 +555,8 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -577,13 +586,13 @@
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>6</v>
+      <c r="B4" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="9">
         <v>1</v>
@@ -591,10 +600,10 @@
     </row>
     <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>8</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -846,17 +855,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EF093B-66D8-481C-9675-90EBD4EEB36E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9422D5EA-73A0-40E6-A4A6-69DD3F347630}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
     <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E051536C-7B99-4C3A-887E-8FAA0EACB30C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9445F9E-B9AB-4F91-9AED-B4975EA91DF6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -875,7 +885,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A75D7A-0551-486B-B9F6-37F32AA206F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD3AFD5D-B2EB-4B7C-B9D5-F081DC0BCFEF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
